--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/may-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/may-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>25793.56</v>
+        <v>25638.98</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>270.44</v>
+        <v>268.82</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8419.5</v>
+        <v>8369.040000000001</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>978.37</v>
+        <v>972.5</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>16975.31</v>
+        <v>16744.52</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>279.35</v>
+        <v>275.55</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>17802.24</v>
+        <v>17560.21</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>31755.78</v>
+        <v>31324.04</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>756.49</v>
+        <v>746.21</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1670.38</v>
+        <v>1647.67</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>472.38</v>
+        <v>465.95</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8673.43</v>
+        <v>8555.51</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1026.53</v>
+        <v>1012.57</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>668.5700000000001</v>
+        <v>659.48</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>7938.94</v>
+        <v>7831.01</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>226.66</v>
+        <v>223.58</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>974.66</v>
+        <v>961.41</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>661.8099999999999</v>
+        <v>652.8200000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>8619.32</v>
+        <v>8502.139999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5268.67</v>
+        <v>5197.04</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>14347.8</v>
+        <v>14152.74</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>8487.66</v>
+        <v>8372.26</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>16838.09</v>
+        <v>16694.47</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1910.05</v>
+        <v>1893.76</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1188.87</v>
+        <v>1178.73</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>8419.049999999999</v>
+        <v>8347.24</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>870.45</v>
+        <v>863.03</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>306.06</v>
+        <v>303.45</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>8419.049999999999</v>
+        <v>8347.24</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>638.3200000000001</v>
+        <v>632.88</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>937.77</v>
+        <v>929.77</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>360.39</v>
+        <v>357.31</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>9377.65</v>
+        <v>9297.67</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>692.14</v>
+        <v>686.24</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7956.94</v>
+        <v>7889.08</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>10581.75</v>
+        <v>10491.5</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>24070.19</v>
+        <v>23864.89</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1280.54</v>
+        <v>1269.62</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>696.1</v>
+        <v>690.16</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>279.35</v>
+        <v>276.97</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2479.14</v>
+        <v>2457.99</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>209.48</v>
+        <v>207.7</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>8419.049999999999</v>
+        <v>8347.24</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>17802.24</v>
+        <v>17650.4</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1336.57</v>
+        <v>1343.77</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2806.78</v>
+        <v>2821.89</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>456.04</v>
+        <v>458.5</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>11724.5</v>
+        <v>11787.64</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1948.75</v>
+        <v>1959.25</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>515.1799999999999</v>
+        <v>520.9400000000001</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>8619.32</v>
+        <v>8715.719999999999</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1206.85</v>
+        <v>1220.35</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>8487.66</v>
+        <v>8582.58</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>7938.94</v>
+        <v>8027.73</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2655.54</v>
+        <v>2685.24</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>7118.87</v>
+        <v>7198.49</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1286.46</v>
+        <v>1300.85</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3547.25</v>
+        <v>3586.92</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>5100.24</v>
+        <v>5157.28</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>18922.12</v>
+        <v>19065.44</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2560.64</v>
+        <v>2580.03</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>16036.42</v>
+        <v>16157.89</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>193.62</v>
+        <v>195.09</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>8487.66</v>
+        <v>8551.940000000001</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>31755.78</v>
+        <v>31996.31</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>908.89</v>
+        <v>915.77</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>8018.21</v>
+        <v>8078.94</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2767.22</v>
+        <v>2788.18</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>31973.9</v>
+        <v>32216.08</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>928.98</v>
+        <v>936.02</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>5494.74</v>
+        <v>5536.36</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>107.94</v>
+        <v>108.76</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>849.25</v>
+        <v>852.47</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>568.28</v>
+        <v>570.4299999999999</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>8018.21</v>
+        <v>8048.59</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>680.34</v>
+        <v>682.92</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>9139.75</v>
+        <v>9174.379999999999</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>893.04</v>
+        <v>896.4299999999999</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>968.49</v>
+        <v>972.16</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>7938.94</v>
+        <v>7969.02</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>8673.43</v>
+        <v>8706.290000000001</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>9139.75</v>
+        <v>9174.379999999999</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>589.91</v>
+        <v>592.14</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>7938.94</v>
+        <v>7969.02</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>333.04</v>
+        <v>334.3</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>17249.47</v>
+        <v>17314.82</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>319.96</v>
+        <v>321.18</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>15877.89</v>
+        <v>15938.04</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1198.87</v>
+        <v>1203.41</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>150.37</v>
+        <v>150.94</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>8018.21</v>
+        <v>8048.59</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1728.13</v>
+        <v>1734.68</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>15877.89</v>
+        <v>15938.04</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2639.47</v>
+        <v>2649.46</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>871.29</v>
+        <v>874.59</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1162.6</v>
+        <v>1159.66</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2559.56</v>
+        <v>2553.1</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>3654.43</v>
+        <v>3645.2</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1014.2</v>
+        <v>1011.64</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>611.05</v>
+        <v>609.51</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>551.09</v>
+        <v>549.7</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>8619.32</v>
+        <v>8597.559999999999</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>8018.21</v>
+        <v>7997.97</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1140.87</v>
+        <v>1137.99</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>595.35</v>
+        <v>593.85</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>8619.32</v>
+        <v>8597.559999999999</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>684.3</v>
+        <v>682.58</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>632.6</v>
+        <v>631</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1010.74</v>
+        <v>1008.19</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>8018.21</v>
+        <v>7997.97</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>750.24</v>
+        <v>748.35</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>514.75</v>
+        <v>513.45</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>8419.120000000001</v>
+        <v>8499.110000000001</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>631.59</v>
+        <v>637.59</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>9139.75</v>
+        <v>9226.58</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>800.4400000000001</v>
+        <v>808.05</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>7706.73</v>
+        <v>7779.95</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>8419.120000000001</v>
+        <v>8499.110000000001</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>8419.120000000001</v>
+        <v>8499.110000000001</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>8419.120000000001</v>
+        <v>8499.110000000001</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>899.6</v>
+        <v>908.15</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>277.65</v>
+        <v>280.29</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3221.45</v>
+        <v>3252.06</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1905.66</v>
+        <v>1923.76</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>7938.94</v>
+        <v>8014.37</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>9545.450000000001</v>
+        <v>9636.139999999999</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>4231.99</v>
+        <v>4272.2</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>2770.12</v>
+        <v>2796.44</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2445.63</v>
+        <v>2468.86</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>7261.41</v>
+        <v>7330.4</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>5105.01</v>
+        <v>5153.51</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>5105.01</v>
+        <v>5153.51</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>5105.01</v>
+        <v>5153.51</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>5163.48</v>
+        <v>5212.53</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>151.1</v>
+        <v>152.54</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>127.59</v>
+        <v>128.8</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>9692.290000000001</v>
+        <v>9784.379999999999</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>579.21</v>
+        <v>584.71</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>5105.01</v>
+        <v>5153.51</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>553.2</v>
+        <v>557.33</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>15877.89</v>
+        <v>15996.18</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>910.67</v>
+        <v>917.45</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>7938.94</v>
+        <v>7998.09</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1426.43</v>
+        <v>1437.06</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1361.15</v>
+        <v>1371.29</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>848.83</v>
+        <v>855.16</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>697.75</v>
+        <v>702.95</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>8419.120000000001</v>
+        <v>8481.84</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>697.75</v>
+        <v>702.95</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>16038.12</v>
+        <v>16157.6</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1367.78</v>
+        <v>1377.97</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>8419.120000000001</v>
+        <v>8481.84</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>901.16</v>
+        <v>907.87</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>15877.89</v>
+        <v>15996.18</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>692.17</v>
+        <v>697.33</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>8419.120000000001</v>
+        <v>8481.84</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>540.11</v>
+        <v>544.14</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>8471.26</v>
+        <v>8534.370000000001</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>581.3</v>
+        <v>585.63</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>927.64</v>
+        <v>934.55</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>746.17</v>
+        <v>751.73</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>2774.43</v>
+        <v>2795.1</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2051.66</v>
+        <v>2066.94</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>4947.52</v>
+        <v>4984.38</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2782.78</v>
+        <v>2803.51</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>8007.22</v>
+        <v>8066.88</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>2010.29</v>
+        <v>2025.27</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>2394.11</v>
+        <v>2411.95</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>785.8099999999999</v>
+        <v>791.66</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>21208.59</v>
+        <v>21366.6</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1979.01</v>
+        <v>1993.75</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>5699.99</v>
+        <v>5742.45</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>9386.209999999999</v>
+        <v>9456.129999999999</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>5913.61</v>
+        <v>5854.64</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>865.91</v>
+        <v>857.27</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1324.28</v>
+        <v>1311.07</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>8019.06</v>
+        <v>7939.09</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>272.56</v>
+        <v>269.84</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1166.13</v>
+        <v>1154.51</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>963.34</v>
+        <v>953.73</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>8471.26</v>
+        <v>8386.780000000001</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>443.31</v>
+        <v>438.89</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>8419.120000000001</v>
+        <v>8335.16</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>15594.09</v>
+        <v>15438.57</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>8419.120000000001</v>
+        <v>8335.16</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>740.9</v>
+        <v>733.51</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>5167.58</v>
+        <v>5116.05</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>27265.04</v>
+        <v>26993.13</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>8419.120000000001</v>
+        <v>8335.16</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>740.9</v>
+        <v>733.51</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>16838.09</v>
+        <v>16670.17</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>905.89</v>
+        <v>896.86</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>149.53</v>
+        <v>148.03</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>8419.120000000001</v>
+        <v>8335.16</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>689.17</v>
+        <v>682.29</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>450.08</v>
+        <v>445.59</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>9511.74</v>
+        <v>9470.040000000001</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>6348.09</v>
+        <v>6320.27</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>3100.72</v>
+        <v>3087.13</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>3423.37</v>
+        <v>3408.37</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>472.38</v>
+        <v>467.24</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>8471.26</v>
+        <v>8379.110000000001</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>4444.29</v>
+        <v>4395.94</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1091.39</v>
+        <v>1079.52</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>16830.56</v>
+        <v>16647.47</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1424.64</v>
+        <v>1409.14</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>1602.58</v>
+        <v>1585.15</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>6282.23</v>
+        <v>6213.9</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>8673.43</v>
+        <v>8579.08</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>8007.22</v>
+        <v>7920.12</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>9139.75</v>
+        <v>9040.33</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>3046.46</v>
+        <v>3013.32</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>413.35</v>
+        <v>408.85</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1137.1</v>
+        <v>1124.73</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>8415.280000000001</v>
+        <v>8323.73</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>4820.12</v>
+        <v>4767.68</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>12725.66</v>
+        <v>12587.23</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>8018.21</v>
+        <v>7930.99</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>1041.25</v>
+        <v>1029.92</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>59.3</v>
+        <v>58.66</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>9936.93</v>
+        <v>9914.370000000001</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>41082.5</v>
+        <v>40989.25</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>3443.58</v>
+        <v>3435.07</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1513.97</v>
+        <v>1510.23</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>1703.36</v>
+        <v>1699.16</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>851.21</v>
+        <v>849.11</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>8018.21</v>
+        <v>7998.41</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>937.65</v>
+        <v>935.33</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>8471.26</v>
+        <v>8450.34</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>712.11</v>
+        <v>710.35</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>8619.32</v>
+        <v>8598.040000000001</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>551.09</v>
+        <v>549.73</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>4533.29</v>
+        <v>4522.1</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>29919.54</v>
+        <v>30066.51</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>809.98</v>
+        <v>813.96</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>560.1900000000001</v>
+        <v>562.9400000000001</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>1391.31</v>
+        <v>1398.14</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>3209.47</v>
+        <v>3225.23</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>8471.26</v>
+        <v>8512.870000000001</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>8419.049999999999</v>
+        <v>8460.4</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>6128.86</v>
+        <v>6158.96</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>680.34</v>
+        <v>683.6900000000001</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>56295.87</v>
+        <v>56572.41</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1068.78</v>
+        <v>1074.03</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>139.67</v>
+        <v>140.14</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>8471.26</v>
+        <v>8499.360000000001</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>361.42</v>
+        <v>362.62</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1090.85</v>
+        <v>1094.47</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>901.84</v>
+        <v>904.83</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>8419.049999999999</v>
+        <v>8446.969999999999</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>858.64</v>
+        <v>861.49</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>8471.26</v>
+        <v>8499.360000000001</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>2447.31</v>
+        <v>2455.42</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>631.7</v>
+        <v>633.8</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>1765.22</v>
+        <v>1770.84</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>676.34</v>
+        <v>678.49</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>2781.78</v>
+        <v>2790.63</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>16830.56</v>
+        <v>16884.12</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1262.58</v>
+        <v>1266.6</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>8007.22</v>
+        <v>8032.71</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>16830.56</v>
+        <v>16884.12</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>590.78</v>
+        <v>592.66</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>8415.280000000001</v>
+        <v>8442.059999999999</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>676.83</v>
+        <v>678.99</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1663.72</v>
+        <v>1672.56</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>1927.97</v>
+        <v>1938.22</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>16830.56</v>
+        <v>16920.05</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>8619.32</v>
+        <v>8665.15</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1187.3</v>
+        <v>1193.62</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>16830.56</v>
+        <v>16920.05</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>692.26</v>
+        <v>695.9400000000001</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>8419.049999999999</v>
+        <v>8463.809999999999</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>8419.049999999999</v>
+        <v>8463.809999999999</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>8007.22</v>
+        <v>8049.8</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>8471.26</v>
+        <v>8516.309999999999</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>8007.22</v>
+        <v>8049.8</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>25901.79</v>
+        <v>26039.52</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>924.3</v>
+        <v>929.21</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>7938.94</v>
+        <v>7981.16</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>612.66</v>
+        <v>615.92</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>501.12</v>
+        <v>503.78</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>21243.12</v>
+        <v>21356.08</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>707.16</v>
+        <v>710.92</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>922.37</v>
+        <v>927.28</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>2180.67</v>
+        <v>2192.27</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/may-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/may-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/may-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/may-2026.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO MAYORISTA METROPOLITANO</t>
+          <t>supermercado mayorista metropolitano</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10853,7 +10853,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11656,7 +11656,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12022,7 +12022,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12327,7 +12327,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -12368,7 +12368,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13100,7 +13100,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13608,7 +13608,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14086,7 +14086,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14503,7 +14503,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -14513,7 +14513,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14564,7 +14564,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15062,7 +15062,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15113,7 +15113,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15184,7 +15184,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15235,7 +15235,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15357,7 +15357,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15418,7 +15418,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15479,7 +15479,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15601,7 +15601,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15723,7 +15723,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -15733,7 +15733,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -15916,7 +15916,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16221,7 +16221,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16231,7 +16231,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -16282,7 +16282,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16343,7 +16343,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -16455,7 +16455,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -16465,7 +16465,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16516,7 +16516,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -16526,7 +16526,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -16536,7 +16536,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -16577,7 +16577,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -16587,7 +16587,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16638,7 +16638,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16709,7 +16709,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16760,7 +16760,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -16780,7 +16780,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -16821,7 +16821,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -16943,7 +16943,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -16953,7 +16953,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -16963,7 +16963,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -17004,7 +17004,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17065,7 +17065,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17126,7 +17126,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17197,7 +17197,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17248,7 +17248,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -17258,7 +17258,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17380,7 +17380,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17502,7 +17502,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -17563,7 +17563,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -17685,7 +17685,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -17736,7 +17736,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -17746,7 +17746,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17807,7 +17807,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>DIRECCION DE INFANCIA</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/may-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/may-2026.xlsx
@@ -562,7 +562,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.102.347-0</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1318,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1383,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1509,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1574,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2493,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2741,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2806,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2871,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2936,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3001,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3127,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3314,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3379,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3444,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3509,11 @@
           <t>77.942.697-1</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3574,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4066,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4253,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4318,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4444,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4631,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4818,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +4944,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5070,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5135,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5383,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5448,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5696,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5822,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5887,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +5952,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6078,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6143,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6269,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6395,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6460,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6647,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6712,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6777,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7025,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7212,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7277,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7342,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7529,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7655,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7781,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7846,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8155,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8403,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8468,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8533,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8598,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8663,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +8972,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9037,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9102,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9167,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9293,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9541,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9606,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9671,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9736,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9862,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +9988,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10114,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10240,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10366,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10492,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10557,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10622,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11053,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11118,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11305,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11370,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11496,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11561,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11687,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +11813,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12183,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12248,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12435,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12561,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12626,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +12813,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +12878,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +12943,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13008,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13073,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13321,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13508,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13573,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +13821,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +13886,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +13951,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14077,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14142,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14268,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14333,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14459,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14585,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14650,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14715,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +14841,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +14967,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15154,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15707,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +15833,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +15898,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16024,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16272,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16398,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16585,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +16955,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17081,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17146,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17516,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +17947,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18256,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +18382,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/may-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/may-2026.xlsx
@@ -2652,7 +2652,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -15313,7 +15313,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -15435,7 +15435,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -16122,7 +16122,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -16496,7 +16496,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -17183,7 +17183,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -17858,7 +17858,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
